--- a/outputs/tables/n_eleitos_federais.xlsx
+++ b/outputs/tables/n_eleitos_federais.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denis\Desktop\TCC\TCC_arvore\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TCC_Denis_git\outputs\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA33FC22-B8F0-4EB3-9DE5-DC44DDE7B8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7601352-D943-4939-8389-EC6B3CCA6C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>ANO_ELEICAO</t>
   </si>
@@ -36,27 +36,12 @@
   <si>
     <t>TOTAL</t>
   </si>
-  <si>
-    <t>Ano</t>
-  </si>
-  <si>
-    <t>Religiosos eleitos</t>
-  </si>
-  <si>
-    <t>Seguranças eleitos</t>
-  </si>
-  <si>
-    <t>Total eleitos</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,12 +55,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -85,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -108,49 +87,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -461,7 +406,7 @@
     <col min="5" max="5" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -475,7 +420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2014</v>
       </c>
@@ -489,7 +434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2018</v>
       </c>
@@ -503,7 +448,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2022</v>
       </c>
@@ -517,7 +462,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -528,76 +473,6 @@
         <v>76</v>
       </c>
       <c r="D5">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>2014</v>
-      </c>
-      <c r="C11" s="3">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="2">
-        <v>2018</v>
-      </c>
-      <c r="C12" s="3">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3">
-        <v>28</v>
-      </c>
-      <c r="E12" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
-        <v>2022</v>
-      </c>
-      <c r="C13" s="3">
-        <v>10</v>
-      </c>
-      <c r="D13" s="3">
-        <v>34</v>
-      </c>
-      <c r="E13" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>25</v>
-      </c>
-      <c r="D14" s="7">
-        <v>76</v>
-      </c>
-      <c r="E14" s="7">
         <v>101</v>
       </c>
     </row>
